--- a/Email_Generation_Template.xlsx
+++ b/Email_Generation_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dHat\Documents\GitHub\ezeeMsgMake\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE637528-FE6D-4E16-948B-C1067FCEA56D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6023B0CA-5DDF-4FB8-986A-236CF41D3F7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Email_Generation_Template.xlsx
+++ b/Email_Generation_Template.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dHat\Documents\GitHub\ezeeMsgMake\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F1849A1-AA7B-4EF3-B4F5-A0B7E8953E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B83FBCB7-51C6-47A8-8862-96857530005F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="16668" windowHeight="8748" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$L$140</definedName>
@@ -28,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="261">
   <si>
     <t>First Name</t>
   </si>
@@ -66,10 +68,751 @@
     <t>Trimmed Last Name</t>
   </si>
   <si>
+    <t>Jamie</t>
+  </si>
+  <si>
     <t>FirstLast@</t>
   </si>
   <si>
-    <t>scotiabank.com</t>
+    <t>David</t>
+  </si>
+  <si>
+    <t>Lisa</t>
+  </si>
+  <si>
+    <t>Stephanie</t>
+  </si>
+  <si>
+    <t>Carlos</t>
+  </si>
+  <si>
+    <t>Curtis</t>
+  </si>
+  <si>
+    <t>Adam</t>
+  </si>
+  <si>
+    <t>Erin</t>
+  </si>
+  <si>
+    <t>Brian</t>
+  </si>
+  <si>
+    <t>Rahul</t>
+  </si>
+  <si>
+    <t>Dennis</t>
+  </si>
+  <si>
+    <t>Deanna</t>
+  </si>
+  <si>
+    <t>Nancy</t>
+  </si>
+  <si>
+    <t>Jane</t>
+  </si>
+  <si>
+    <t>Arfat</t>
+  </si>
+  <si>
+    <t>Virakti</t>
+  </si>
+  <si>
+    <t>Tomi</t>
+  </si>
+  <si>
+    <t>Rebecca</t>
+  </si>
+  <si>
+    <t>Rodney</t>
+  </si>
+  <si>
+    <t>Leaira</t>
+  </si>
+  <si>
+    <t>Michelle</t>
+  </si>
+  <si>
+    <t>Martha</t>
+  </si>
+  <si>
+    <t>Shannon</t>
+  </si>
+  <si>
+    <t>Jeff</t>
+  </si>
+  <si>
+    <t>Kirstin</t>
+  </si>
+  <si>
+    <t>Gloria</t>
+  </si>
+  <si>
+    <t>Lucas</t>
+  </si>
+  <si>
+    <t>Raylene</t>
+  </si>
+  <si>
+    <t>Leilani</t>
+  </si>
+  <si>
+    <t>Kristina</t>
+  </si>
+  <si>
+    <t>Brett</t>
+  </si>
+  <si>
+    <t>Kevin</t>
+  </si>
+  <si>
+    <t>Nina</t>
+  </si>
+  <si>
+    <t>Brianne</t>
+  </si>
+  <si>
+    <t>Nicole</t>
+  </si>
+  <si>
+    <t>Bebee</t>
+  </si>
+  <si>
+    <t>Nikki</t>
+  </si>
+  <si>
+    <t>Tanya</t>
+  </si>
+  <si>
+    <t>Mikayla</t>
+  </si>
+  <si>
+    <t>Agnes</t>
+  </si>
+  <si>
+    <t>Fiona</t>
+  </si>
+  <si>
+    <t>Susan</t>
+  </si>
+  <si>
+    <t>Connie</t>
+  </si>
+  <si>
+    <t>Elaina</t>
+  </si>
+  <si>
+    <t>Holly</t>
+  </si>
+  <si>
+    <t>Surong</t>
+  </si>
+  <si>
+    <t>Jaskirat</t>
+  </si>
+  <si>
+    <t>Chioma</t>
+  </si>
+  <si>
+    <t>Petra</t>
+  </si>
+  <si>
+    <t>Seitz</t>
+  </si>
+  <si>
+    <t>Knox</t>
+  </si>
+  <si>
+    <t>Janine</t>
+  </si>
+  <si>
+    <t>Karishma</t>
+  </si>
+  <si>
+    <t>Danna</t>
+  </si>
+  <si>
+    <t>Lauretta</t>
+  </si>
+  <si>
+    <t>Bruce</t>
+  </si>
+  <si>
+    <t>Meghan</t>
+  </si>
+  <si>
+    <t>Olanrewaju</t>
+  </si>
+  <si>
+    <t>Phil</t>
+  </si>
+  <si>
+    <t>Spencer</t>
+  </si>
+  <si>
+    <t>Angela</t>
+  </si>
+  <si>
+    <t>Becky</t>
+  </si>
+  <si>
+    <t>Bob</t>
+  </si>
+  <si>
+    <t>Laurie</t>
+  </si>
+  <si>
+    <t>Owais</t>
+  </si>
+  <si>
+    <t>Kelsey</t>
+  </si>
+  <si>
+    <t>Shelley</t>
+  </si>
+  <si>
+    <t>Lindsay</t>
+  </si>
+  <si>
+    <t>Wanda</t>
+  </si>
+  <si>
+    <t>Nichola</t>
+  </si>
+  <si>
+    <t>Blair</t>
+  </si>
+  <si>
+    <t>Mayela</t>
+  </si>
+  <si>
+    <t>Torri</t>
+  </si>
+  <si>
+    <t>Dana</t>
+  </si>
+  <si>
+    <t>Shane</t>
+  </si>
+  <si>
+    <t>Nav</t>
+  </si>
+  <si>
+    <t>Teresa</t>
+  </si>
+  <si>
+    <t>Gaurang</t>
+  </si>
+  <si>
+    <t>Wendy</t>
+  </si>
+  <si>
+    <t>Jennifer</t>
+  </si>
+  <si>
+    <t>Chelsea</t>
+  </si>
+  <si>
+    <t>Madeline</t>
+  </si>
+  <si>
+    <t>Suzy</t>
+  </si>
+  <si>
+    <t>Saqib</t>
+  </si>
+  <si>
+    <t>Shanna</t>
+  </si>
+  <si>
+    <t>Kyla</t>
+  </si>
+  <si>
+    <t>Sclina</t>
+  </si>
+  <si>
+    <t>Kathryn</t>
+  </si>
+  <si>
+    <t>Deirdra</t>
+  </si>
+  <si>
+    <t>Neil</t>
+  </si>
+  <si>
+    <t>Jacqueline</t>
+  </si>
+  <si>
+    <t>Jodi</t>
+  </si>
+  <si>
+    <t>Channing</t>
+  </si>
+  <si>
+    <t>Rupal</t>
+  </si>
+  <si>
+    <t>jane.bogatyrevich@atco.com</t>
+  </si>
+  <si>
+    <t>arfat.anwar@atco.com</t>
+  </si>
+  <si>
+    <t>virakti.anjaria@atco.com</t>
+  </si>
+  <si>
+    <t>tomi.owoyemi@atco.com</t>
+  </si>
+  <si>
+    <t>rebecca.white@atco.com</t>
+  </si>
+  <si>
+    <t>erin.jackson@atco.com</t>
+  </si>
+  <si>
+    <t>rodney.deir@atco.com</t>
+  </si>
+  <si>
+    <t>leaira.isley@atco.com</t>
+  </si>
+  <si>
+    <t>michelle.paterson@atco.com</t>
+  </si>
+  <si>
+    <t>martha.wasylynchuk@atco.com</t>
+  </si>
+  <si>
+    <t>shannon.rittmeyer@atco.com</t>
+  </si>
+  <si>
+    <t>jeff.ferguson@atco.com</t>
+  </si>
+  <si>
+    <t>kirstin.normand@atco.com</t>
+  </si>
+  <si>
+    <t>gloria.bhatia@atco.com</t>
+  </si>
+  <si>
+    <t>lucas.janke@atco.com</t>
+  </si>
+  <si>
+    <t>raylene.frehlich@atco.com</t>
+  </si>
+  <si>
+    <t>leilani.coralejo@atco.com</t>
+  </si>
+  <si>
+    <t>kristina.clayton@atco.com</t>
+  </si>
+  <si>
+    <t>brett.eigner@atco.com</t>
+  </si>
+  <si>
+    <t>kevin.lazarenko@atco.com</t>
+  </si>
+  <si>
+    <t>nina.edwards@atco.com</t>
+  </si>
+  <si>
+    <t>brianne.rainey@atco.com</t>
+  </si>
+  <si>
+    <t>nicole.maclean@atco.com</t>
+  </si>
+  <si>
+    <t>rahul.chinta@atco.com</t>
+  </si>
+  <si>
+    <t>bebee.chang@atco.com</t>
+  </si>
+  <si>
+    <t>nancy.lewis@atco.com</t>
+  </si>
+  <si>
+    <t>nikki.gjerde@atco.com</t>
+  </si>
+  <si>
+    <t>tanya.danielson@atco.com</t>
+  </si>
+  <si>
+    <t>mikayla.smetaniuk@atco.com</t>
+  </si>
+  <si>
+    <t>agnes.hickey@atco.com</t>
+  </si>
+  <si>
+    <t>fiona.broadhead@atco.com</t>
+  </si>
+  <si>
+    <t>susan.elliott@atco.com</t>
+  </si>
+  <si>
+    <t>deanna.girard@atco.com</t>
+  </si>
+  <si>
+    <t>connie.berkshire@atco.com</t>
+  </si>
+  <si>
+    <t>elaina.eifler@atco.com</t>
+  </si>
+  <si>
+    <t>holly.hutchinson@atco.com</t>
+  </si>
+  <si>
+    <t>surong.wang@atco.com</t>
+  </si>
+  <si>
+    <t>jaskirat.kalsi@atco.com</t>
+  </si>
+  <si>
+    <t>chioma.ahaneku@atco.com</t>
+  </si>
+  <si>
+    <t>petra.seitz@atco.com</t>
+  </si>
+  <si>
+    <t>knox.davidson@atco.com</t>
+  </si>
+  <si>
+    <t>janine.tornhout@atco.com</t>
+  </si>
+  <si>
+    <t>karishma.arora@atco.com</t>
+  </si>
+  <si>
+    <t>lisa.nyman@atco.com</t>
+  </si>
+  <si>
+    <t>danna.richardson@atco.com</t>
+  </si>
+  <si>
+    <t>lauretta.pearse@atco.com</t>
+  </si>
+  <si>
+    <t>bruce.legault@atco.com</t>
+  </si>
+  <si>
+    <t>meghan.stuart@atco.com</t>
+  </si>
+  <si>
+    <t>olanrewaju.oyelami@atco.com</t>
+  </si>
+  <si>
+    <t>phil.atherton@atco.com</t>
+  </si>
+  <si>
+    <t>spencer.forgo@atco.com</t>
+  </si>
+  <si>
+    <t>tanya.cake@atco.com</t>
+  </si>
+  <si>
+    <t>angela.nordstrom@atco.com</t>
+  </si>
+  <si>
+    <t>Becky.Penrice@atco.com</t>
+  </si>
+  <si>
+    <t>Brian.Bain@atco.com</t>
+  </si>
+  <si>
+    <t>Bob.Myles@atco.com</t>
+  </si>
+  <si>
+    <t>Laurie.Bos@atco.com</t>
+  </si>
+  <si>
+    <t>Owais.Khan@atco.com</t>
+  </si>
+  <si>
+    <t>Kelsey.Trovato@atco.com</t>
+  </si>
+  <si>
+    <t>Nancy.Manchak@atco.com</t>
+  </si>
+  <si>
+    <t>Jamie.Jaques@atco.com</t>
+  </si>
+  <si>
+    <t>Shelley.Faria@atco.com</t>
+  </si>
+  <si>
+    <t>Lindsay.Angelstad@atco.com</t>
+  </si>
+  <si>
+    <t>Wanda.Hulme@atco.com</t>
+  </si>
+  <si>
+    <t>Nichola.Belsheim@atco.com</t>
+  </si>
+  <si>
+    <t>Blair.Bishop@atco.com</t>
+  </si>
+  <si>
+    <t>Mayela.Neubert@atco.com</t>
+  </si>
+  <si>
+    <t>Torri.Lamash@atco.com</t>
+  </si>
+  <si>
+    <t>Dennis.Gilson@atco.com</t>
+  </si>
+  <si>
+    <t>Brett.Heath@atco.com</t>
+  </si>
+  <si>
+    <t>Dana.Johansen@atco.com</t>
+  </si>
+  <si>
+    <t>Shane.Ellis@atco.com</t>
+  </si>
+  <si>
+    <t>Nav.Basra@atco.com</t>
+  </si>
+  <si>
+    <t>Teresa.Smith@atco.com</t>
+  </si>
+  <si>
+    <t>Gaurang.Vyas@atco.com</t>
+  </si>
+  <si>
+    <t>Wendy.Armstrong@atco.com</t>
+  </si>
+  <si>
+    <t>Jennifer.Hadada@atco.com</t>
+  </si>
+  <si>
+    <t>Chelsea.Keelan@atco.com</t>
+  </si>
+  <si>
+    <t>Madeline.Dey@atco.com</t>
+  </si>
+  <si>
+    <t>David.Chiasson@atco.com</t>
+  </si>
+  <si>
+    <t>Suzy.Connolly@atco.com</t>
+  </si>
+  <si>
+    <t>Jennifer.Stinson@atco.com</t>
+  </si>
+  <si>
+    <t>David.Peterson@atco.com</t>
+  </si>
+  <si>
+    <t>Saqib.Iqbal@atco.com</t>
+  </si>
+  <si>
+    <t>Shanna.Jaap@atco.com</t>
+  </si>
+  <si>
+    <t>Adam.Wallace@atco.com</t>
+  </si>
+  <si>
+    <t>Kyla.Jenkinson@atco.com</t>
+  </si>
+  <si>
+    <t>Sclina.Lau@atco.com</t>
+  </si>
+  <si>
+    <t>Kathryn.Dickson@atco.com</t>
+  </si>
+  <si>
+    <t>Carlos.Bautista@atco.com</t>
+  </si>
+  <si>
+    <t>Deirdra.McLaughlin@atco.com</t>
+  </si>
+  <si>
+    <t>Neil.Orr@atco.com</t>
+  </si>
+  <si>
+    <t>Wendy.Chenier@atco.com</t>
+  </si>
+  <si>
+    <t>Jacqueline.Cunha@atco.com</t>
+  </si>
+  <si>
+    <t>Jodi.Collier@atco.com</t>
+  </si>
+  <si>
+    <t>Channing.Steinbring@atco.com</t>
+  </si>
+  <si>
+    <t>Rupal.Shah@atco.com</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Sarah</t>
+  </si>
+  <si>
+    <t>Sharmeen</t>
+  </si>
+  <si>
+    <t>Billy</t>
+  </si>
+  <si>
+    <t>Grey</t>
+  </si>
+  <si>
+    <t>Veronica</t>
+  </si>
+  <si>
+    <t>Tasha</t>
+  </si>
+  <si>
+    <t>Aynsley</t>
+  </si>
+  <si>
+    <t>Aashna</t>
+  </si>
+  <si>
+    <t>Cole</t>
+  </si>
+  <si>
+    <t>Samrat</t>
+  </si>
+  <si>
+    <t>Nicky</t>
+  </si>
+  <si>
+    <t>Hilda</t>
+  </si>
+  <si>
+    <t>Layla</t>
+  </si>
+  <si>
+    <t>Siobhan</t>
+  </si>
+  <si>
+    <t>Opemipo</t>
+  </si>
+  <si>
+    <t>Ankira</t>
+  </si>
+  <si>
+    <t>Karen</t>
+  </si>
+  <si>
+    <t>Ariba</t>
+  </si>
+  <si>
+    <t>canadalife.com</t>
+  </si>
+  <si>
+    <t>kevin.laljie@canadalife.com</t>
+  </si>
+  <si>
+    <t>sharmeen.malik@canadalife.com</t>
+  </si>
+  <si>
+    <t>billy.stewart@canadalife.com</t>
+  </si>
+  <si>
+    <t>grey.nutter@canadalife.com</t>
+  </si>
+  <si>
+    <t>veronica.desrosiers@canadalife.com</t>
+  </si>
+  <si>
+    <t>tasha.kokinasidis@canadalife.com</t>
+  </si>
+  <si>
+    <t>aynsley.hamilton@canadalife.com</t>
+  </si>
+  <si>
+    <t>aashna.singh@canadalife.com</t>
+  </si>
+  <si>
+    <t>cole.higgins@canadalife.com</t>
+  </si>
+  <si>
+    <t>samrat.paul@canadalife.com</t>
+  </si>
+  <si>
+    <t>nicky.leach@canadalife.com</t>
+  </si>
+  <si>
+    <t>hilda.vallapuram@canadalife.com</t>
+  </si>
+  <si>
+    <t>stephanie.anderson@canadalife.com</t>
+  </si>
+  <si>
+    <t>layla.acharoui@canadalife.com</t>
+  </si>
+  <si>
+    <t>siobhan.oneill@canadalife.com</t>
+  </si>
+  <si>
+    <t>opemipo.obaido@canadalife.com</t>
+  </si>
+  <si>
+    <t>ankira.arora@canadalife.com</t>
+  </si>
+  <si>
+    <t>nikki.vieira@canadalife.com</t>
+  </si>
+  <si>
+    <t>karen.leadbeater@canadalife.com</t>
+  </si>
+  <si>
+    <t>ariba.malik@canadalife.com</t>
+  </si>
+  <si>
+    <t>Justin</t>
+  </si>
+  <si>
+    <t>Krulicki</t>
+  </si>
+  <si>
+    <t>Reeder</t>
+  </si>
+  <si>
+    <t>Julia</t>
+  </si>
+  <si>
+    <t>Mamone</t>
+  </si>
+  <si>
+    <t>Arisha</t>
+  </si>
+  <si>
+    <t>Issani</t>
+  </si>
+  <si>
+    <t>Mohammed</t>
+  </si>
+  <si>
+    <t>Gary</t>
+  </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>Chloe</t>
+  </si>
+  <si>
+    <t>McCann</t>
+  </si>
+  <si>
+    <t>Omara</t>
+  </si>
+  <si>
+    <t>Jake</t>
+  </si>
+  <si>
+    <t>Walker</t>
+  </si>
+  <si>
+    <t>Kristopher</t>
+  </si>
+  <si>
+    <t>Bates</t>
   </si>
 </sst>
 </file>
@@ -484,421 +1227,493 @@
         <v>9</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>13</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B3" t="s">
+        <v>245</v>
+      </c>
       <c r="C3" t="str">
         <f>IF(A3&lt;&gt;"",TRIM(A3),"")</f>
-        <v/>
+        <v>Justin</v>
       </c>
       <c r="D3" t="str">
         <f>IF(B3&lt;&gt;"",TRIM(B3),"")</f>
-        <v/>
+        <v>Krulicki</v>
       </c>
       <c r="E3" t="str">
         <f>IF($C3&lt;&gt;"",LOWER(CONCATENATE(LEFT($C3,1),E$1,$D3,"@",$L$2)),"")</f>
-        <v/>
+        <v>j.krulicki@canadalife.com</v>
       </c>
       <c r="F3" t="str">
         <f>IF($C3&lt;&gt;"",LOWER((CONCATENATE($C3,F$1,$D3,"@",$L$2))),"")</f>
-        <v/>
+        <v>justin.krulicki@canadalife.com</v>
       </c>
       <c r="G3" t="str">
         <f t="shared" ref="G3:H19" si="0">IF($C3&lt;&gt;"",LOWER(CONCATENATE(LEFT($C3,1),G$1,$D3,"@",$L$2)),"")</f>
-        <v/>
+        <v>jkrulicki@canadalife.com</v>
       </c>
       <c r="H3" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>j_krulicki@canadalife.com</v>
       </c>
       <c r="I3" t="str">
         <f>IF($C3&lt;&gt;"",LOWER(CONCATENATE($C3,I$1,$D3,"@",$L$2)),"")</f>
-        <v/>
+        <v>justin_krulicki@canadalife.com</v>
       </c>
       <c r="J3" t="str">
         <f>IF($C3&lt;&gt;"",LOWER(CONCATENATE($C3,J$1,$D3,"@",$L$2)),"")</f>
-        <v/>
+        <v>justinkrulicki@canadalife.com</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" t="s">
+        <v>246</v>
+      </c>
       <c r="C4" t="str">
         <f t="shared" ref="C4:C11" si="1">IF(A4&lt;&gt;"",TRIM(A4),"")</f>
-        <v/>
+        <v>Jennifer</v>
       </c>
       <c r="D4" t="str">
         <f t="shared" ref="D4:D11" si="2">IF(B4&lt;&gt;"",TRIM(B4),"")</f>
-        <v/>
+        <v>Reeder</v>
       </c>
       <c r="E4" t="str">
         <f t="shared" ref="E4:E54" si="3">IF($C4&lt;&gt;"",LOWER(CONCATENATE(LEFT($C4,1),E$1,$D4,"@",$L$2)),"")</f>
-        <v/>
+        <v>j.reeder@canadalife.com</v>
       </c>
       <c r="F4" t="str">
         <f t="shared" ref="F4:F54" si="4">IF($C4&lt;&gt;"",LOWER((CONCATENATE($C4,F$1,$D4,"@",$L$2))),"")</f>
-        <v/>
+        <v>jennifer.reeder@canadalife.com</v>
       </c>
       <c r="G4" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>jreeder@canadalife.com</v>
       </c>
       <c r="H4" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>j_reeder@canadalife.com</v>
       </c>
       <c r="I4" t="str">
         <f t="shared" ref="I4:J54" si="5">IF($C4&lt;&gt;"",LOWER(CONCATENATE($C4,I$1,$D4,"@",$L$2)),"")</f>
-        <v/>
+        <v>jennifer_reeder@canadalife.com</v>
       </c>
       <c r="J4" t="str">
         <f>IF($C4&lt;&gt;"",LOWER(CONCATENATE($C4,J$1,$D4,"@",$L$2)),"")</f>
-        <v/>
+        <v>jenniferreeder@canadalife.com</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>247</v>
+      </c>
+      <c r="B5" t="s">
+        <v>248</v>
+      </c>
       <c r="C5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Julia</v>
       </c>
       <c r="D5" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Mamone</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>j.mamone@canadalife.com</v>
       </c>
       <c r="F5" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>julia.mamone@canadalife.com</v>
       </c>
       <c r="G5" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>jmamone@canadalife.com</v>
       </c>
       <c r="H5" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>j_mamone@canadalife.com</v>
       </c>
       <c r="I5" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>julia_mamone@canadalife.com</v>
       </c>
       <c r="J5" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>juliamamone@canadalife.com</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>249</v>
+      </c>
+      <c r="B6" t="s">
+        <v>250</v>
+      </c>
       <c r="C6" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Arisha</v>
       </c>
       <c r="D6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Issani</v>
       </c>
       <c r="E6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>a.issani@canadalife.com</v>
       </c>
       <c r="F6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>arisha.issani@canadalife.com</v>
       </c>
       <c r="G6" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>aissani@canadalife.com</v>
       </c>
       <c r="H6" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>a_issani@canadalife.com</v>
       </c>
       <c r="I6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>arisha_issani@canadalife.com</v>
       </c>
       <c r="J6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>arishaissani@canadalife.com</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>244</v>
+      </c>
+      <c r="B7" t="s">
+        <v>251</v>
+      </c>
       <c r="C7" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Justin</v>
       </c>
       <c r="D7" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Mohammed</v>
       </c>
       <c r="E7" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>j.mohammed@canadalife.com</v>
       </c>
       <c r="F7" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>justin.mohammed@canadalife.com</v>
       </c>
       <c r="G7" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>jmohammed@canadalife.com</v>
       </c>
       <c r="H7" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>j_mohammed@canadalife.com</v>
       </c>
       <c r="I7" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>justin_mohammed@canadalife.com</v>
       </c>
       <c r="J7" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>justinmohammed@canadalife.com</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>252</v>
+      </c>
+      <c r="B8" t="s">
+        <v>253</v>
+      </c>
       <c r="C8" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Gary</v>
       </c>
       <c r="D8" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Good</v>
       </c>
       <c r="E8" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>g.good@canadalife.com</v>
       </c>
       <c r="F8" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>gary.good@canadalife.com</v>
       </c>
       <c r="G8" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>ggood@canadalife.com</v>
       </c>
       <c r="H8" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>g_good@canadalife.com</v>
       </c>
       <c r="I8" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>gary_good@canadalife.com</v>
       </c>
       <c r="J8" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>garygood@canadalife.com</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
       <c r="C9" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Chelsea</v>
       </c>
       <c r="D9" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Curtis</v>
       </c>
       <c r="E9" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>c.curtis@canadalife.com</v>
       </c>
       <c r="F9" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>chelsea.curtis@canadalife.com</v>
       </c>
       <c r="G9" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>ccurtis@canadalife.com</v>
       </c>
       <c r="H9" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>c_curtis@canadalife.com</v>
       </c>
       <c r="I9" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>chelsea_curtis@canadalife.com</v>
       </c>
       <c r="J9" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>chelseacurtis@canadalife.com</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" t="s">
+        <v>62</v>
+      </c>
       <c r="C10" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Jennifer</v>
       </c>
       <c r="D10" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Seitz</v>
       </c>
       <c r="E10" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>j.seitz@canadalife.com</v>
       </c>
       <c r="F10" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>jennifer.seitz@canadalife.com</v>
       </c>
       <c r="G10" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>jseitz@canadalife.com</v>
       </c>
       <c r="H10" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>j_seitz@canadalife.com</v>
       </c>
       <c r="I10" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>jennifer_seitz@canadalife.com</v>
       </c>
       <c r="J10" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>jenniferseitz@canadalife.com</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>254</v>
+      </c>
+      <c r="B11" t="s">
+        <v>255</v>
+      </c>
       <c r="C11" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Chloe</v>
       </c>
       <c r="D11" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>McCann</v>
       </c>
       <c r="E11" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>c.mccann@canadalife.com</v>
       </c>
       <c r="F11" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>chloe.mccann@canadalife.com</v>
       </c>
       <c r="G11" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>cmccann@canadalife.com</v>
       </c>
       <c r="H11" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>c_mccann@canadalife.com</v>
       </c>
       <c r="I11" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>chloe_mccann@canadalife.com</v>
       </c>
       <c r="J11" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>chloemccann@canadalife.com</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>205</v>
+      </c>
+      <c r="B12" t="s">
+        <v>256</v>
+      </c>
       <c r="C12" t="str">
         <f>IF(A12&lt;&gt;"",TRIM(A12),"")</f>
-        <v/>
+        <v>Sarah</v>
       </c>
       <c r="D12" t="str">
         <f>IF(B12&lt;&gt;"",TRIM(B12),"")</f>
-        <v/>
+        <v>Omara</v>
       </c>
       <c r="E12" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>s.omara@canadalife.com</v>
       </c>
       <c r="F12" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>sarah.omara@canadalife.com</v>
       </c>
       <c r="G12" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>somara@canadalife.com</v>
       </c>
       <c r="H12" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>s_omara@canadalife.com</v>
       </c>
       <c r="I12" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>sarah_omara@canadalife.com</v>
       </c>
       <c r="J12" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>sarahomara@canadalife.com</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>257</v>
+      </c>
+      <c r="B13" t="s">
+        <v>258</v>
+      </c>
       <c r="C13" t="str">
         <f t="shared" ref="C13:C22" si="6">IF(A13&lt;&gt;"",TRIM(A13),"")</f>
-        <v/>
+        <v>Jake</v>
       </c>
       <c r="D13" t="str">
         <f t="shared" ref="D13:D22" si="7">IF(B13&lt;&gt;"",TRIM(B13),"")</f>
-        <v/>
+        <v>Walker</v>
       </c>
       <c r="E13" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>j.walker@canadalife.com</v>
       </c>
       <c r="F13" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>jake.walker@canadalife.com</v>
       </c>
       <c r="G13" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>jwalker@canadalife.com</v>
       </c>
       <c r="H13" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>j_walker@canadalife.com</v>
       </c>
       <c r="I13" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>jake_walker@canadalife.com</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>jakewalker@canadalife.com</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>259</v>
+      </c>
+      <c r="B14" t="s">
+        <v>260</v>
+      </c>
       <c r="C14" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>Kristopher</v>
       </c>
       <c r="D14" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>Bates</v>
       </c>
       <c r="E14" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>k.bates@canadalife.com</v>
       </c>
       <c r="F14" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>kristopher.bates@canadalife.com</v>
       </c>
       <c r="G14" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>kbates@canadalife.com</v>
       </c>
       <c r="H14" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>k_bates@canadalife.com</v>
       </c>
       <c r="I14" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>kristopher_bates@canadalife.com</v>
       </c>
       <c r="J14" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>kristopherbates@canadalife.com</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
@@ -5131,4 +5946,1763 @@
     <ignoredError sqref="F3" formula="1"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48221E54-6CBD-4FAE-86C8-E398090CA7F2}">
+  <dimension ref="A1:B138"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>209</v>
+      </c>
+      <c r="B5" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>210</v>
+      </c>
+      <c r="B6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>211</v>
+      </c>
+      <c r="B7" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>212</v>
+      </c>
+      <c r="B8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>213</v>
+      </c>
+      <c r="B9" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>214</v>
+      </c>
+      <c r="B10" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>215</v>
+      </c>
+      <c r="B11" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>216</v>
+      </c>
+      <c r="B12" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>217</v>
+      </c>
+      <c r="B14" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>218</v>
+      </c>
+      <c r="B15" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>219</v>
+      </c>
+      <c r="B16" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>220</v>
+      </c>
+      <c r="B17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>221</v>
+      </c>
+      <c r="B19" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>222</v>
+      </c>
+      <c r="B20" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B32" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B33" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B34" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B35" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B36" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B37" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B38" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B39" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B40" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B41" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B42" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B43" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B44" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B45" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B46" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B47" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B48" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B49" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B50" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B51" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B52" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B53" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B54" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B55" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B56" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B57" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B58" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B59" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B60" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="61" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B61" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B62" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B63" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="64" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B64" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B65" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B66" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B67" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B68" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B69" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B70" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B71" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B72" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B73" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B74" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B75" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B76" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B77" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="78" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B78" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="79" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B79" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="80" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B80" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="81" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B81" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="82" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B82" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B83" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B84" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="85" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B85" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="86" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B86" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="87" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B87" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="88" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B88" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="89" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B89" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="90" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B90" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="91" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B91" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="92" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B92" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="93" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B93" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="94" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B94" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="95" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B95" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="96" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B96" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="97" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B97" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B98" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="99" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B99" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B100" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="101" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B101" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B102" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="103" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B103" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="104" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B104" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="105" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B105" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="106" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B106" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="107" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B107" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B108" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B109" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="110" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B110" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B111" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="112" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B112" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B113" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B114" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B115" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B116" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="117" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B117" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B118" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B119" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B120" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B121" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="122" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B122" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B123" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B124" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="125" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B125" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="126" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B126" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="127" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B127" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="128" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B128" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B129" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B130" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B131" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="132" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B132" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="133" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B133" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="134" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B134" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="135" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B135" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="136" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B136" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="137" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B137" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B138" t="s">
+        <v>204</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CBBBE82-E138-48AF-9B2B-AB1EE6ED354A}">
+  <dimension ref="A1:B139"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>50</v>
+      </c>
+      <c r="B29" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>53</v>
+      </c>
+      <c r="B32" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>24</v>
+      </c>
+      <c r="B34" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>55</v>
+      </c>
+      <c r="B35" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>56</v>
+      </c>
+      <c r="B36" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>57</v>
+      </c>
+      <c r="B37" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>58</v>
+      </c>
+      <c r="B38" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>59</v>
+      </c>
+      <c r="B39" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>60</v>
+      </c>
+      <c r="B40" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>61</v>
+      </c>
+      <c r="B41" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>63</v>
+      </c>
+      <c r="B42" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>64</v>
+      </c>
+      <c r="B43" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>65</v>
+      </c>
+      <c r="B44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>66</v>
+      </c>
+      <c r="B46" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>67</v>
+      </c>
+      <c r="B47" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>68</v>
+      </c>
+      <c r="B48" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>69</v>
+      </c>
+      <c r="B49" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>70</v>
+      </c>
+      <c r="B50" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>71</v>
+      </c>
+      <c r="B51" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>72</v>
+      </c>
+      <c r="B52" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>50</v>
+      </c>
+      <c r="B53" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>73</v>
+      </c>
+      <c r="B54" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>74</v>
+      </c>
+      <c r="B55" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>21</v>
+      </c>
+      <c r="B56" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>75</v>
+      </c>
+      <c r="B57" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>76</v>
+      </c>
+      <c r="B58" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>77</v>
+      </c>
+      <c r="B59" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>78</v>
+      </c>
+      <c r="B60" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>25</v>
+      </c>
+      <c r="B61" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>12</v>
+      </c>
+      <c r="B62" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>79</v>
+      </c>
+      <c r="B63" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>80</v>
+      </c>
+      <c r="B64" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>81</v>
+      </c>
+      <c r="B65" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>82</v>
+      </c>
+      <c r="B66" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>83</v>
+      </c>
+      <c r="B67" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>84</v>
+      </c>
+      <c r="B68" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>85</v>
+      </c>
+      <c r="B69" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>23</v>
+      </c>
+      <c r="B70" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>43</v>
+      </c>
+      <c r="B71" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>86</v>
+      </c>
+      <c r="B72" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>87</v>
+      </c>
+      <c r="B73" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>88</v>
+      </c>
+      <c r="B74" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>89</v>
+      </c>
+      <c r="B75" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>90</v>
+      </c>
+      <c r="B76" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>91</v>
+      </c>
+      <c r="B77" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>92</v>
+      </c>
+      <c r="B78" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>93</v>
+      </c>
+      <c r="B79" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>94</v>
+      </c>
+      <c r="B80" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>14</v>
+      </c>
+      <c r="B81" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>95</v>
+      </c>
+      <c r="B82" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>92</v>
+      </c>
+      <c r="B83" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>14</v>
+      </c>
+      <c r="B84" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>96</v>
+      </c>
+      <c r="B85" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>97</v>
+      </c>
+      <c r="B86" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>19</v>
+      </c>
+      <c r="B87" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>98</v>
+      </c>
+      <c r="B88" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>99</v>
+      </c>
+      <c r="B89" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>100</v>
+      </c>
+      <c r="B90" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>17</v>
+      </c>
+      <c r="B91" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>101</v>
+      </c>
+      <c r="B92" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>102</v>
+      </c>
+      <c r="B93" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>91</v>
+      </c>
+      <c r="B94" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>103</v>
+      </c>
+      <c r="B95" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>104</v>
+      </c>
+      <c r="B96" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>105</v>
+      </c>
+      <c r="B97" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>106</v>
+      </c>
+      <c r="B98" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B99" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B100" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B101" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B102" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B103" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B104" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B105" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B106" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B107" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B108" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B109" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B110" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B111" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B112" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B113" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B114" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B115" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B116" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="117" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B117" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B118" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B119" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B120" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B121" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="122" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B122" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B123" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B124" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="125" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B125" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="126" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B126" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="127" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B127" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="128" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B128" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B129" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B130" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B131" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="132" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B132" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="133" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B133" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="134" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B134" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="135" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B135" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="136" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B136" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="137" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B137" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B138" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="139" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B139" t="s">
+        <v>204</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Email_Generation_Template.xlsx
+++ b/Email_Generation_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dHat\Documents\GitHub\ezeeMsgMake\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97763577-9E8A-4003-955C-405B9BB85B48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0DC304C-1893-42B7-B66F-EAD4AAC3D90A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$O$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$O$119</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="46">
   <si>
     <t>First Name</t>
   </si>
@@ -75,127 +75,97 @@
     <t>First@</t>
   </si>
   <si>
-    <t>HR Business Partner</t>
+    <t>Lee</t>
   </si>
   <si>
-    <t>Senior Business Analyst</t>
+    <t>Anjali</t>
   </si>
   <si>
-    <t>Alex</t>
+    <t>Mehta</t>
   </si>
   <si>
-    <t>Neelaveni</t>
-  </si>
-  <si>
-    <t>Senthilkumar</t>
-  </si>
-  <si>
-    <t>Project Manager IT Infrastructure and Security</t>
-  </si>
-  <si>
-    <t>Daniel</t>
-  </si>
-  <si>
-    <t>Reader</t>
-  </si>
-  <si>
-    <t>Information Security Specialist</t>
-  </si>
-  <si>
-    <t>Suadik</t>
-  </si>
-  <si>
-    <t>Braimah</t>
-  </si>
-  <si>
-    <t>Cyber Security Advocate</t>
-  </si>
-  <si>
-    <t>Bob</t>
-  </si>
-  <si>
-    <t>Moskal</t>
-  </si>
-  <si>
-    <t>Manager of Security</t>
-  </si>
-  <si>
-    <t>Richard</t>
-  </si>
-  <si>
-    <t>Dela Cruz</t>
-  </si>
-  <si>
-    <t>IT Support Specialist</t>
-  </si>
-  <si>
-    <t>Diego</t>
-  </si>
-  <si>
-    <t>Garavito</t>
-  </si>
-  <si>
-    <t>Senior Developer Enterprise Systems</t>
-  </si>
-  <si>
-    <t>George</t>
-  </si>
-  <si>
-    <t>Campian</t>
-  </si>
-  <si>
-    <t>Amal</t>
-  </si>
-  <si>
-    <t>Hapuarachchi</t>
-  </si>
-  <si>
-    <t>ERP Software Developer</t>
-  </si>
-  <si>
-    <t>Putman</t>
-  </si>
-  <si>
-    <t>Head of Talent Acquisition</t>
-  </si>
-  <si>
-    <t>Marleni</t>
-  </si>
-  <si>
-    <t>Rosario</t>
-  </si>
-  <si>
-    <t>Talent Acquisition Manager</t>
-  </si>
-  <si>
-    <t>Haley</t>
-  </si>
-  <si>
-    <t>Walls</t>
-  </si>
-  <si>
-    <t>Lidya</t>
-  </si>
-  <si>
-    <t>Gonzalez</t>
-  </si>
-  <si>
-    <t>Human Resource Manager</t>
-  </si>
-  <si>
-    <t>Mike</t>
-  </si>
-  <si>
-    <t>McDaniel</t>
-  </si>
-  <si>
-    <t>Vice President Human Resources</t>
-  </si>
-  <si>
-    <t>priceindustries.com</t>
+    <t>HR Advisor</t>
   </si>
   <si>
     <t>FirstL@</t>
+  </si>
+  <si>
+    <t>M.</t>
+  </si>
+  <si>
+    <t>diligent.com</t>
+  </si>
+  <si>
+    <t>Simha</t>
+  </si>
+  <si>
+    <t>Reddy</t>
+  </si>
+  <si>
+    <t>Cyber Defense Leader / SecOps / IR / AppSec</t>
+  </si>
+  <si>
+    <t>Christopher</t>
+  </si>
+  <si>
+    <t>SecOps leadership</t>
+  </si>
+  <si>
+    <t>Paulo</t>
+  </si>
+  <si>
+    <t>Amaral</t>
+  </si>
+  <si>
+    <t>Cybersecurity Leader | AI Governance &amp; GRC Automation</t>
+  </si>
+  <si>
+    <t>Technology Risk, Audit &amp; Compliance</t>
+  </si>
+  <si>
+    <t>Peymaneh</t>
+  </si>
+  <si>
+    <t>Chychi</t>
+  </si>
+  <si>
+    <t>GRC SaaS / FedRAMP / CMMC GTM</t>
+  </si>
+  <si>
+    <t>Žarko</t>
+  </si>
+  <si>
+    <t>Cumpf</t>
+  </si>
+  <si>
+    <t>GRC / Vendor Management / FedRAMP sales leadership</t>
+  </si>
+  <si>
+    <t>Paul</t>
+  </si>
+  <si>
+    <t>Solutions Engineer</t>
+  </si>
+  <si>
+    <t>Sadie</t>
+  </si>
+  <si>
+    <t>Wilson</t>
+  </si>
+  <si>
+    <t>Solutions Engineer II</t>
+  </si>
+  <si>
+    <t>Lili</t>
+  </si>
+  <si>
+    <t>Varga</t>
+  </si>
+  <si>
+    <t>Nicky</t>
+  </si>
+  <si>
+    <t>Senior HRBP</t>
   </si>
 </sst>
 </file>
@@ -566,7 +536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O124"/>
+  <dimension ref="A1:O119"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20.77734375" bestFit="1" customWidth="1"/>
@@ -638,685 +608,658 @@
         <v>12</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="N2" s="4" t="s">
         <v>2</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D3" t="str">
         <f>IF(A3&lt;&gt;"",TRIM(A3),"")</f>
-        <v>Neelaveni</v>
+        <v>Simha</v>
       </c>
       <c r="E3" t="str">
         <f>IF(B3&lt;&gt;"",TRIM(B3),"")</f>
-        <v>Senthilkumar</v>
+        <v>Reddy</v>
       </c>
       <c r="F3" t="str">
         <f>IF($D3&lt;&gt;"",_xlfn.CONCAT(A3,"@",$O$2),"")</f>
-        <v>Neelaveni@priceindustries.com</v>
+        <v>Simha@diligent.com</v>
       </c>
       <c r="G3" t="str">
         <f>IF($D3&lt;&gt;"",LOWER(CONCATENATE(LEFT($D3,1),G$1,$E3,"@",$O$2)),"")</f>
-        <v>n.senthilkumar@priceindustries.com</v>
+        <v>s.reddy@diligent.com</v>
       </c>
       <c r="H3" t="str">
         <f>IF($D3&lt;&gt;"",LOWER((CONCATENATE($D3,H$1,$E3,"@",$O$2))),"")</f>
-        <v>neelaveni.senthilkumar@priceindustries.com</v>
+        <v>simha.reddy@diligent.com</v>
       </c>
       <c r="I3" t="str">
         <f>IF($D3&lt;&gt;"",LOWER(CONCATENATE(LEFT($D3,1),I$1,$E3,"@",$O$2)),"")</f>
-        <v>nsenthilkumar@priceindustries.com</v>
+        <v>sreddy@diligent.com</v>
       </c>
       <c r="J3" t="str">
         <f>IF($D3&lt;&gt;"",LOWER(CONCATENATE(LEFT($D3,1),J$1,$E3,"@",$O$2)),"")</f>
-        <v>n_senthilkumar@priceindustries.com</v>
+        <v>s_reddy@diligent.com</v>
       </c>
       <c r="K3" t="str">
         <f>IF($D3&lt;&gt;"",LOWER(CONCATENATE($D3,K$1,$E3,"@",$O$2)),"")</f>
-        <v>neelaveni_senthilkumar@priceindustries.com</v>
+        <v>simha_reddy@diligent.com</v>
       </c>
       <c r="L3" t="str">
         <f>IF($D3&lt;&gt;"",LOWER(CONCATENATE($D3,L$1,$E3,"@",$O$2)),"")</f>
-        <v>neelavenisenthilkumar@priceindustries.com</v>
+        <v>simhareddy@diligent.com</v>
       </c>
       <c r="M3" t="str">
         <f>IF($D3&lt;&gt;"",LOWER(CONCATENATE($D3,M$1,LEFT($E3,1),"@",$O$2)),"")</f>
-        <v>neelavenis@priceindustries.com</v>
+        <v>simhar@diligent.com</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D4" t="str">
-        <f t="shared" ref="D4:D8" si="0">IF(A4&lt;&gt;"",TRIM(A4),"")</f>
-        <v>Daniel</v>
+        <f t="shared" ref="D4:D7" si="0">IF(A4&lt;&gt;"",TRIM(A4),"")</f>
+        <v>Christopher</v>
       </c>
       <c r="E4" t="str">
-        <f t="shared" ref="E4:E8" si="1">IF(B4&lt;&gt;"",TRIM(B4),"")</f>
-        <v>Reader</v>
+        <f t="shared" ref="E4:E7" si="1">IF(B4&lt;&gt;"",TRIM(B4),"")</f>
+        <v>M.</v>
       </c>
       <c r="F4" t="str">
         <f>IF($D4&lt;&gt;"",_xlfn.CONCAT(A4,"@",$O$2),"")</f>
-        <v>Daniel@priceindustries.com</v>
+        <v>Christopher@diligent.com</v>
       </c>
       <c r="G4" t="str">
         <f>IF($D4&lt;&gt;"",LOWER(CONCATENATE(LEFT($D4,1),G$1,$E4,"@",$O$2)),"")</f>
-        <v>d.reader@priceindustries.com</v>
+        <v>c.m.@diligent.com</v>
       </c>
       <c r="H4" t="str">
         <f>IF($D4&lt;&gt;"",LOWER((CONCATENATE($D4,H$1,$E4,"@",$O$2))),"")</f>
-        <v>daniel.reader@priceindustries.com</v>
+        <v>christopher.m.@diligent.com</v>
       </c>
       <c r="I4" t="str">
         <f>IF($D4&lt;&gt;"",LOWER(CONCATENATE(LEFT($D4,1),I$1,$E4,"@",$O$2)),"")</f>
-        <v>dreader@priceindustries.com</v>
+        <v>cm.@diligent.com</v>
       </c>
       <c r="J4" t="str">
         <f>IF($D4&lt;&gt;"",LOWER(CONCATENATE(LEFT($D4,1),J$1,$E4,"@",$O$2)),"")</f>
-        <v>d_reader@priceindustries.com</v>
+        <v>c_m.@diligent.com</v>
       </c>
       <c r="K4" t="str">
         <f>IF($D4&lt;&gt;"",LOWER(CONCATENATE($D4,K$1,$E4,"@",$O$2)),"")</f>
-        <v>daniel_reader@priceindustries.com</v>
+        <v>christopher_m.@diligent.com</v>
       </c>
       <c r="L4" t="str">
         <f>IF($D4&lt;&gt;"",LOWER(CONCATENATE($D4,L$1,$E4,"@",$O$2)),"")</f>
-        <v>danielreader@priceindustries.com</v>
+        <v>christopherm.@diligent.com</v>
       </c>
       <c r="M4" t="str">
-        <f t="shared" ref="M4:M67" si="2">IF($D4&lt;&gt;"",LOWER(CONCATENATE($D4,M$1,LEFT($E4,1),"@",$O$2)),"")</f>
-        <v>danielr@priceindustries.com</v>
+        <f t="shared" ref="M4:M62" si="2">IF($D4&lt;&gt;"",LOWER(CONCATENATE($D4,M$1,LEFT($E4,1),"@",$O$2)),"")</f>
+        <v>christopherm@diligent.com</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D5" t="str">
         <f t="shared" si="0"/>
-        <v>Suadik</v>
+        <v>Paulo</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" si="1"/>
-        <v>Braimah</v>
+        <v>Amaral</v>
       </c>
       <c r="F5" t="str">
         <f>IF($D5&lt;&gt;"",_xlfn.CONCAT(A5,"@",$O$2),"")</f>
-        <v>Suadik@priceindustries.com</v>
+        <v>Paulo@diligent.com</v>
       </c>
       <c r="G5" t="str">
         <f>IF($D5&lt;&gt;"",LOWER(CONCATENATE(LEFT($D5,1),G$1,$E5,"@",$O$2)),"")</f>
-        <v>s.braimah@priceindustries.com</v>
+        <v>p.amaral@diligent.com</v>
       </c>
       <c r="H5" t="str">
         <f>IF($D5&lt;&gt;"",LOWER((CONCATENATE($D5,H$1,$E5,"@",$O$2))),"")</f>
-        <v>suadik.braimah@priceindustries.com</v>
+        <v>paulo.amaral@diligent.com</v>
       </c>
       <c r="I5" t="str">
         <f>IF($D5&lt;&gt;"",LOWER(CONCATENATE(LEFT($D5,1),I$1,$E5,"@",$O$2)),"")</f>
-        <v>sbraimah@priceindustries.com</v>
+        <v>pamaral@diligent.com</v>
       </c>
       <c r="J5" t="str">
         <f>IF($D5&lt;&gt;"",LOWER(CONCATENATE(LEFT($D5,1),J$1,$E5,"@",$O$2)),"")</f>
-        <v>s_braimah@priceindustries.com</v>
+        <v>p_amaral@diligent.com</v>
       </c>
       <c r="K5" t="str">
         <f>IF($D5&lt;&gt;"",LOWER(CONCATENATE($D5,K$1,$E5,"@",$O$2)),"")</f>
-        <v>suadik_braimah@priceindustries.com</v>
+        <v>paulo_amaral@diligent.com</v>
       </c>
       <c r="L5" t="str">
         <f>IF($D5&lt;&gt;"",LOWER(CONCATENATE($D5,L$1,$E5,"@",$O$2)),"")</f>
-        <v>suadikbraimah@priceindustries.com</v>
+        <v>pauloamaral@diligent.com</v>
       </c>
       <c r="M5" t="str">
         <f t="shared" si="2"/>
-        <v>suadikb@priceindustries.com</v>
+        <v>pauloa@diligent.com</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6" t="str">
         <f t="shared" si="0"/>
-        <v>Bob</v>
+        <v>Anjali</v>
       </c>
       <c r="E6" t="str">
         <f t="shared" si="1"/>
-        <v>Moskal</v>
+        <v>Mehta</v>
       </c>
       <c r="F6" t="str">
         <f>IF($D6&lt;&gt;"",_xlfn.CONCAT(A6,"@",$O$2),"")</f>
-        <v>Bob@priceindustries.com</v>
+        <v>Anjali@diligent.com</v>
       </c>
       <c r="G6" t="str">
         <f>IF($D6&lt;&gt;"",LOWER(CONCATENATE(LEFT($D6,1),G$1,$E6,"@",$O$2)),"")</f>
-        <v>b.moskal@priceindustries.com</v>
+        <v>a.mehta@diligent.com</v>
       </c>
       <c r="H6" t="str">
         <f>IF($D6&lt;&gt;"",LOWER((CONCATENATE($D6,H$1,$E6,"@",$O$2))),"")</f>
-        <v>bob.moskal@priceindustries.com</v>
+        <v>anjali.mehta@diligent.com</v>
       </c>
       <c r="I6" t="str">
         <f>IF($D6&lt;&gt;"",LOWER(CONCATENATE(LEFT($D6,1),I$1,$E6,"@",$O$2)),"")</f>
-        <v>bmoskal@priceindustries.com</v>
+        <v>amehta@diligent.com</v>
       </c>
       <c r="J6" t="str">
         <f>IF($D6&lt;&gt;"",LOWER(CONCATENATE(LEFT($D6,1),J$1,$E6,"@",$O$2)),"")</f>
-        <v>b_moskal@priceindustries.com</v>
+        <v>a_mehta@diligent.com</v>
       </c>
       <c r="K6" t="str">
         <f>IF($D6&lt;&gt;"",LOWER(CONCATENATE($D6,K$1,$E6,"@",$O$2)),"")</f>
-        <v>bob_moskal@priceindustries.com</v>
+        <v>anjali_mehta@diligent.com</v>
       </c>
       <c r="L6" t="str">
         <f>IF($D6&lt;&gt;"",LOWER(CONCATENATE($D6,L$1,$E6,"@",$O$2)),"")</f>
-        <v>bobmoskal@priceindustries.com</v>
+        <v>anjalimehta@diligent.com</v>
       </c>
       <c r="M6" t="str">
         <f t="shared" si="2"/>
-        <v>bobm@priceindustries.com</v>
+        <v>anjalim@diligent.com</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D7" t="str">
         <f t="shared" si="0"/>
-        <v>Richard</v>
+        <v>Peymaneh</v>
       </c>
       <c r="E7" t="str">
         <f t="shared" si="1"/>
-        <v>Dela Cruz</v>
+        <v>Chychi</v>
       </c>
       <c r="F7" t="str">
         <f>IF($D7&lt;&gt;"",_xlfn.CONCAT(A7,"@",$O$2),"")</f>
-        <v>Richard@priceindustries.com</v>
+        <v>Peymaneh@diligent.com</v>
       </c>
       <c r="G7" t="str">
         <f>IF($D7&lt;&gt;"",LOWER(CONCATENATE(LEFT($D7,1),G$1,$E7,"@",$O$2)),"")</f>
-        <v>r.dela cruz@priceindustries.com</v>
+        <v>p.chychi@diligent.com</v>
       </c>
       <c r="H7" t="str">
         <f>IF($D7&lt;&gt;"",LOWER((CONCATENATE($D7,H$1,$E7,"@",$O$2))),"")</f>
-        <v>richard.dela cruz@priceindustries.com</v>
+        <v>peymaneh.chychi@diligent.com</v>
       </c>
       <c r="I7" t="str">
         <f>IF($D7&lt;&gt;"",LOWER(CONCATENATE(LEFT($D7,1),I$1,$E7,"@",$O$2)),"")</f>
-        <v>rdela cruz@priceindustries.com</v>
+        <v>pchychi@diligent.com</v>
       </c>
       <c r="J7" t="str">
         <f>IF($D7&lt;&gt;"",LOWER(CONCATENATE(LEFT($D7,1),J$1,$E7,"@",$O$2)),"")</f>
-        <v>r_dela cruz@priceindustries.com</v>
+        <v>p_chychi@diligent.com</v>
       </c>
       <c r="K7" t="str">
         <f>IF($D7&lt;&gt;"",LOWER(CONCATENATE($D7,K$1,$E7,"@",$O$2)),"")</f>
-        <v>richard_dela cruz@priceindustries.com</v>
+        <v>peymaneh_chychi@diligent.com</v>
       </c>
       <c r="L7" t="str">
         <f>IF($D7&lt;&gt;"",LOWER(CONCATENATE($D7,L$1,$E7,"@",$O$2)),"")</f>
-        <v>richarddela cruz@priceindustries.com</v>
+        <v>peymanehchychi@diligent.com</v>
       </c>
       <c r="M7" t="str">
         <f t="shared" si="2"/>
-        <v>richardd@priceindustries.com</v>
+        <v>peymanehc@diligent.com</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D8" t="str">
-        <f t="shared" si="0"/>
-        <v>Diego</v>
+        <f t="shared" ref="D8:D11" si="3">IF(A8&lt;&gt;"",TRIM(A8),"")</f>
+        <v>Žarko</v>
       </c>
       <c r="E8" t="str">
-        <f t="shared" si="1"/>
-        <v>Garavito</v>
+        <f t="shared" ref="E8:E11" si="4">IF(B8&lt;&gt;"",TRIM(B8),"")</f>
+        <v>Cumpf</v>
       </c>
       <c r="F8" t="str">
         <f>IF($D8&lt;&gt;"",_xlfn.CONCAT(A8,"@",$O$2),"")</f>
-        <v>Diego@priceindustries.com</v>
+        <v>Žarko@diligent.com</v>
       </c>
       <c r="G8" t="str">
         <f>IF($D8&lt;&gt;"",LOWER(CONCATENATE(LEFT($D8,1),G$1,$E8,"@",$O$2)),"")</f>
-        <v>d.garavito@priceindustries.com</v>
+        <v>ž.cumpf@diligent.com</v>
       </c>
       <c r="H8" t="str">
         <f>IF($D8&lt;&gt;"",LOWER((CONCATENATE($D8,H$1,$E8,"@",$O$2))),"")</f>
-        <v>diego.garavito@priceindustries.com</v>
+        <v>žarko.cumpf@diligent.com</v>
       </c>
       <c r="I8" t="str">
         <f>IF($D8&lt;&gt;"",LOWER(CONCATENATE(LEFT($D8,1),I$1,$E8,"@",$O$2)),"")</f>
-        <v>dgaravito@priceindustries.com</v>
+        <v>žcumpf@diligent.com</v>
       </c>
       <c r="J8" t="str">
         <f>IF($D8&lt;&gt;"",LOWER(CONCATENATE(LEFT($D8,1),J$1,$E8,"@",$O$2)),"")</f>
-        <v>d_garavito@priceindustries.com</v>
+        <v>ž_cumpf@diligent.com</v>
       </c>
       <c r="K8" t="str">
         <f>IF($D8&lt;&gt;"",LOWER(CONCATENATE($D8,K$1,$E8,"@",$O$2)),"")</f>
-        <v>diego_garavito@priceindustries.com</v>
+        <v>žarko_cumpf@diligent.com</v>
       </c>
       <c r="L8" t="str">
         <f>IF($D8&lt;&gt;"",LOWER(CONCATENATE($D8,L$1,$E8,"@",$O$2)),"")</f>
-        <v>diegogaravito@priceindustries.com</v>
+        <v>žarkocumpf@diligent.com</v>
       </c>
       <c r="M8" t="str">
         <f t="shared" si="2"/>
-        <v>diegog@priceindustries.com</v>
+        <v>žarkoc@diligent.com</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="D9" t="str">
-        <f>IF(A9&lt;&gt;"",TRIM(A9),"")</f>
-        <v>George</v>
+        <f t="shared" si="3"/>
+        <v>Paul</v>
       </c>
       <c r="E9" t="str">
-        <f>IF(B9&lt;&gt;"",TRIM(B9),"")</f>
-        <v>Campian</v>
+        <f t="shared" si="4"/>
+        <v>Lee</v>
       </c>
       <c r="F9" t="str">
         <f>IF($D9&lt;&gt;"",_xlfn.CONCAT(A9,"@",$O$2),"")</f>
-        <v>George@priceindustries.com</v>
+        <v>Paul@diligent.com</v>
       </c>
       <c r="G9" t="str">
         <f>IF($D9&lt;&gt;"",LOWER(CONCATENATE(LEFT($D9,1),G$1,$E9,"@",$O$2)),"")</f>
-        <v>g.campian@priceindustries.com</v>
+        <v>p.lee@diligent.com</v>
       </c>
       <c r="H9" t="str">
         <f>IF($D9&lt;&gt;"",LOWER((CONCATENATE($D9,H$1,$E9,"@",$O$2))),"")</f>
-        <v>george.campian@priceindustries.com</v>
+        <v>paul.lee@diligent.com</v>
       </c>
       <c r="I9" t="str">
         <f>IF($D9&lt;&gt;"",LOWER(CONCATENATE(LEFT($D9,1),I$1,$E9,"@",$O$2)),"")</f>
-        <v>gcampian@priceindustries.com</v>
+        <v>plee@diligent.com</v>
       </c>
       <c r="J9" t="str">
         <f>IF($D9&lt;&gt;"",LOWER(CONCATENATE(LEFT($D9,1),J$1,$E9,"@",$O$2)),"")</f>
-        <v>g_campian@priceindustries.com</v>
+        <v>p_lee@diligent.com</v>
       </c>
       <c r="K9" t="str">
         <f>IF($D9&lt;&gt;"",LOWER(CONCATENATE($D9,K$1,$E9,"@",$O$2)),"")</f>
-        <v>george_campian@priceindustries.com</v>
+        <v>paul_lee@diligent.com</v>
       </c>
       <c r="L9" t="str">
         <f>IF($D9&lt;&gt;"",LOWER(CONCATENATE($D9,L$1,$E9,"@",$O$2)),"")</f>
-        <v>georgecampian@priceindustries.com</v>
+        <v>paullee@diligent.com</v>
       </c>
       <c r="M9" t="str">
         <f t="shared" si="2"/>
-        <v>georgec@priceindustries.com</v>
+        <v>paull@diligent.com</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D10" t="str">
-        <f t="shared" ref="D10:D16" si="3">IF(A10&lt;&gt;"",TRIM(A10),"")</f>
-        <v>Amal</v>
+        <f t="shared" si="3"/>
+        <v>Sadie</v>
       </c>
       <c r="E10" t="str">
-        <f t="shared" ref="E10:E16" si="4">IF(B10&lt;&gt;"",TRIM(B10),"")</f>
-        <v>Hapuarachchi</v>
+        <f t="shared" si="4"/>
+        <v>Wilson</v>
       </c>
       <c r="F10" t="str">
         <f>IF($D10&lt;&gt;"",_xlfn.CONCAT(A10,"@",$O$2),"")</f>
-        <v>Amal@priceindustries.com</v>
+        <v>Sadie@diligent.com</v>
       </c>
       <c r="G10" t="str">
         <f>IF($D10&lt;&gt;"",LOWER(CONCATENATE(LEFT($D10,1),G$1,$E10,"@",$O$2)),"")</f>
-        <v>a.hapuarachchi@priceindustries.com</v>
+        <v>s.wilson@diligent.com</v>
       </c>
       <c r="H10" t="str">
         <f>IF($D10&lt;&gt;"",LOWER((CONCATENATE($D10,H$1,$E10,"@",$O$2))),"")</f>
-        <v>amal.hapuarachchi@priceindustries.com</v>
+        <v>sadie.wilson@diligent.com</v>
       </c>
       <c r="I10" t="str">
         <f>IF($D10&lt;&gt;"",LOWER(CONCATENATE(LEFT($D10,1),I$1,$E10,"@",$O$2)),"")</f>
-        <v>ahapuarachchi@priceindustries.com</v>
+        <v>swilson@diligent.com</v>
       </c>
       <c r="J10" t="str">
         <f>IF($D10&lt;&gt;"",LOWER(CONCATENATE(LEFT($D10,1),J$1,$E10,"@",$O$2)),"")</f>
-        <v>a_hapuarachchi@priceindustries.com</v>
+        <v>s_wilson@diligent.com</v>
       </c>
       <c r="K10" t="str">
         <f>IF($D10&lt;&gt;"",LOWER(CONCATENATE($D10,K$1,$E10,"@",$O$2)),"")</f>
-        <v>amal_hapuarachchi@priceindustries.com</v>
+        <v>sadie_wilson@diligent.com</v>
       </c>
       <c r="L10" t="str">
         <f>IF($D10&lt;&gt;"",LOWER(CONCATENATE($D10,L$1,$E10,"@",$O$2)),"")</f>
-        <v>amalhapuarachchi@priceindustries.com</v>
+        <v>sadiewilson@diligent.com</v>
       </c>
       <c r="M10" t="str">
         <f t="shared" si="2"/>
-        <v>amalh@priceindustries.com</v>
+        <v>sadiew@diligent.com</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="D11" t="str">
         <f t="shared" si="3"/>
-        <v>Alex</v>
+        <v>Lili</v>
       </c>
       <c r="E11" t="str">
         <f t="shared" si="4"/>
-        <v>Putman</v>
+        <v>Varga</v>
       </c>
       <c r="F11" t="str">
         <f>IF($D11&lt;&gt;"",_xlfn.CONCAT(A11,"@",$O$2),"")</f>
-        <v>Alex@priceindustries.com</v>
+        <v>Lili@diligent.com</v>
       </c>
       <c r="G11" t="str">
         <f>IF($D11&lt;&gt;"",LOWER(CONCATENATE(LEFT($D11,1),G$1,$E11,"@",$O$2)),"")</f>
-        <v>a.putman@priceindustries.com</v>
+        <v>l.varga@diligent.com</v>
       </c>
       <c r="H11" t="str">
         <f>IF($D11&lt;&gt;"",LOWER((CONCATENATE($D11,H$1,$E11,"@",$O$2))),"")</f>
-        <v>alex.putman@priceindustries.com</v>
+        <v>lili.varga@diligent.com</v>
       </c>
       <c r="I11" t="str">
         <f>IF($D11&lt;&gt;"",LOWER(CONCATENATE(LEFT($D11,1),I$1,$E11,"@",$O$2)),"")</f>
-        <v>aputman@priceindustries.com</v>
+        <v>lvarga@diligent.com</v>
       </c>
       <c r="J11" t="str">
         <f>IF($D11&lt;&gt;"",LOWER(CONCATENATE(LEFT($D11,1),J$1,$E11,"@",$O$2)),"")</f>
-        <v>a_putman@priceindustries.com</v>
+        <v>l_varga@diligent.com</v>
       </c>
       <c r="K11" t="str">
         <f>IF($D11&lt;&gt;"",LOWER(CONCATENATE($D11,K$1,$E11,"@",$O$2)),"")</f>
-        <v>alex_putman@priceindustries.com</v>
+        <v>lili_varga@diligent.com</v>
       </c>
       <c r="L11" t="str">
         <f>IF($D11&lt;&gt;"",LOWER(CONCATENATE($D11,L$1,$E11,"@",$O$2)),"")</f>
-        <v>alexputman@priceindustries.com</v>
+        <v>lilivarga@diligent.com</v>
       </c>
       <c r="M11" t="str">
         <f t="shared" si="2"/>
-        <v>alexp@priceindustries.com</v>
+        <v>liliv@diligent.com</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
         <v>45</v>
       </c>
       <c r="D12" t="str">
-        <f t="shared" si="3"/>
-        <v>Marleni</v>
+        <f t="shared" ref="D12:D56" si="5">IF(A12&lt;&gt;"",TRIM(A12),"")</f>
+        <v>Nicky</v>
       </c>
       <c r="E12" t="str">
-        <f t="shared" si="4"/>
-        <v>Rosario</v>
+        <f t="shared" ref="E12:E56" si="6">IF(B12&lt;&gt;"",TRIM(B12),"")</f>
+        <v>Wilson</v>
       </c>
       <c r="F12" t="str">
         <f>IF($D12&lt;&gt;"",_xlfn.CONCAT(A12,"@",$O$2),"")</f>
-        <v>Marleni@priceindustries.com</v>
+        <v>Nicky@diligent.com</v>
       </c>
       <c r="G12" t="str">
         <f>IF($D12&lt;&gt;"",LOWER(CONCATENATE(LEFT($D12,1),G$1,$E12,"@",$O$2)),"")</f>
-        <v>m.rosario@priceindustries.com</v>
+        <v>n.wilson@diligent.com</v>
       </c>
       <c r="H12" t="str">
         <f>IF($D12&lt;&gt;"",LOWER((CONCATENATE($D12,H$1,$E12,"@",$O$2))),"")</f>
-        <v>marleni.rosario@priceindustries.com</v>
+        <v>nicky.wilson@diligent.com</v>
       </c>
       <c r="I12" t="str">
         <f>IF($D12&lt;&gt;"",LOWER(CONCATENATE(LEFT($D12,1),I$1,$E12,"@",$O$2)),"")</f>
-        <v>mrosario@priceindustries.com</v>
+        <v>nwilson@diligent.com</v>
       </c>
       <c r="J12" t="str">
         <f>IF($D12&lt;&gt;"",LOWER(CONCATENATE(LEFT($D12,1),J$1,$E12,"@",$O$2)),"")</f>
-        <v>m_rosario@priceindustries.com</v>
+        <v>n_wilson@diligent.com</v>
       </c>
       <c r="K12" t="str">
         <f>IF($D12&lt;&gt;"",LOWER(CONCATENATE($D12,K$1,$E12,"@",$O$2)),"")</f>
-        <v>marleni_rosario@priceindustries.com</v>
+        <v>nicky_wilson@diligent.com</v>
       </c>
       <c r="L12" t="str">
         <f>IF($D12&lt;&gt;"",LOWER(CONCATENATE($D12,L$1,$E12,"@",$O$2)),"")</f>
-        <v>marlenirosario@priceindustries.com</v>
+        <v>nickywilson@diligent.com</v>
       </c>
       <c r="M12" t="str">
         <f t="shared" si="2"/>
-        <v>marlenir@priceindustries.com</v>
+        <v>nickyw@diligent.com</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" t="s">
-        <v>15</v>
-      </c>
       <c r="D13" t="str">
-        <f t="shared" si="3"/>
-        <v>Haley</v>
+        <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="E13" t="str">
-        <f t="shared" si="4"/>
-        <v>Walls</v>
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="F13" t="str">
         <f>IF($D13&lt;&gt;"",_xlfn.CONCAT(A13,"@",$O$2),"")</f>
-        <v>Haley@priceindustries.com</v>
+        <v/>
       </c>
       <c r="G13" t="str">
         <f>IF($D13&lt;&gt;"",LOWER(CONCATENATE(LEFT($D13,1),G$1,$E13,"@",$O$2)),"")</f>
-        <v>h.walls@priceindustries.com</v>
+        <v/>
       </c>
       <c r="H13" t="str">
         <f>IF($D13&lt;&gt;"",LOWER((CONCATENATE($D13,H$1,$E13,"@",$O$2))),"")</f>
-        <v>haley.walls@priceindustries.com</v>
+        <v/>
       </c>
       <c r="I13" t="str">
         <f>IF($D13&lt;&gt;"",LOWER(CONCATENATE(LEFT($D13,1),I$1,$E13,"@",$O$2)),"")</f>
-        <v>hwalls@priceindustries.com</v>
+        <v/>
       </c>
       <c r="J13" t="str">
         <f>IF($D13&lt;&gt;"",LOWER(CONCATENATE(LEFT($D13,1),J$1,$E13,"@",$O$2)),"")</f>
-        <v>h_walls@priceindustries.com</v>
+        <v/>
       </c>
       <c r="K13" t="str">
         <f>IF($D13&lt;&gt;"",LOWER(CONCATENATE($D13,K$1,$E13,"@",$O$2)),"")</f>
-        <v>haley_walls@priceindustries.com</v>
+        <v/>
       </c>
       <c r="L13" t="str">
         <f>IF($D13&lt;&gt;"",LOWER(CONCATENATE($D13,L$1,$E13,"@",$O$2)),"")</f>
-        <v>haleywalls@priceindustries.com</v>
+        <v/>
       </c>
       <c r="M13" t="str">
         <f t="shared" si="2"/>
-        <v>haleyw@priceindustries.com</v>
+        <v/>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B14" t="s">
-        <v>49</v>
-      </c>
-      <c r="C14" t="s">
-        <v>50</v>
-      </c>
       <c r="D14" t="str">
-        <f t="shared" si="3"/>
-        <v>Lidya</v>
+        <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="E14" t="str">
-        <f t="shared" si="4"/>
-        <v>Gonzalez</v>
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="F14" t="str">
         <f>IF($D14&lt;&gt;"",_xlfn.CONCAT(A14,"@",$O$2),"")</f>
-        <v>Lidya@priceindustries.com</v>
+        <v/>
       </c>
       <c r="G14" t="str">
         <f>IF($D14&lt;&gt;"",LOWER(CONCATENATE(LEFT($D14,1),G$1,$E14,"@",$O$2)),"")</f>
-        <v>l.gonzalez@priceindustries.com</v>
+        <v/>
       </c>
       <c r="H14" t="str">
         <f>IF($D14&lt;&gt;"",LOWER((CONCATENATE($D14,H$1,$E14,"@",$O$2))),"")</f>
-        <v>lidya.gonzalez@priceindustries.com</v>
+        <v/>
       </c>
       <c r="I14" t="str">
         <f>IF($D14&lt;&gt;"",LOWER(CONCATENATE(LEFT($D14,1),I$1,$E14,"@",$O$2)),"")</f>
-        <v>lgonzalez@priceindustries.com</v>
+        <v/>
       </c>
       <c r="J14" t="str">
         <f>IF($D14&lt;&gt;"",LOWER(CONCATENATE(LEFT($D14,1),J$1,$E14,"@",$O$2)),"")</f>
-        <v>l_gonzalez@priceindustries.com</v>
+        <v/>
       </c>
       <c r="K14" t="str">
         <f>IF($D14&lt;&gt;"",LOWER(CONCATENATE($D14,K$1,$E14,"@",$O$2)),"")</f>
-        <v>lidya_gonzalez@priceindustries.com</v>
+        <v/>
       </c>
       <c r="L14" t="str">
         <f>IF($D14&lt;&gt;"",LOWER(CONCATENATE($D14,L$1,$E14,"@",$O$2)),"")</f>
-        <v>lidyagonzalez@priceindustries.com</v>
+        <v/>
       </c>
       <c r="M14" t="str">
         <f t="shared" si="2"/>
-        <v>lidyag@priceindustries.com</v>
+        <v/>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>51</v>
-      </c>
-      <c r="B15" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" t="s">
-        <v>53</v>
-      </c>
       <c r="D15" t="str">
-        <f t="shared" si="3"/>
-        <v>Mike</v>
+        <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="E15" t="str">
-        <f t="shared" si="4"/>
-        <v>McDaniel</v>
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="F15" t="str">
         <f>IF($D15&lt;&gt;"",_xlfn.CONCAT(A15,"@",$O$2),"")</f>
-        <v>Mike@priceindustries.com</v>
+        <v/>
       </c>
       <c r="G15" t="str">
         <f>IF($D15&lt;&gt;"",LOWER(CONCATENATE(LEFT($D15,1),G$1,$E15,"@",$O$2)),"")</f>
-        <v>m.mcdaniel@priceindustries.com</v>
+        <v/>
       </c>
       <c r="H15" t="str">
         <f>IF($D15&lt;&gt;"",LOWER((CONCATENATE($D15,H$1,$E15,"@",$O$2))),"")</f>
-        <v>mike.mcdaniel@priceindustries.com</v>
+        <v/>
       </c>
       <c r="I15" t="str">
         <f>IF($D15&lt;&gt;"",LOWER(CONCATENATE(LEFT($D15,1),I$1,$E15,"@",$O$2)),"")</f>
-        <v>mmcdaniel@priceindustries.com</v>
+        <v/>
       </c>
       <c r="J15" t="str">
         <f>IF($D15&lt;&gt;"",LOWER(CONCATENATE(LEFT($D15,1),J$1,$E15,"@",$O$2)),"")</f>
-        <v>m_mcdaniel@priceindustries.com</v>
+        <v/>
       </c>
       <c r="K15" t="str">
         <f>IF($D15&lt;&gt;"",LOWER(CONCATENATE($D15,K$1,$E15,"@",$O$2)),"")</f>
-        <v>mike_mcdaniel@priceindustries.com</v>
+        <v/>
       </c>
       <c r="L15" t="str">
         <f>IF($D15&lt;&gt;"",LOWER(CONCATENATE($D15,L$1,$E15,"@",$O$2)),"")</f>
-        <v>mikemcdaniel@priceindustries.com</v>
+        <v/>
       </c>
       <c r="M15" t="str">
         <f t="shared" si="2"/>
-        <v>mikem@priceindustries.com</v>
+        <v/>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="D16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="E16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F16" t="str">
@@ -1354,11 +1297,11 @@
     </row>
     <row r="17" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D17" t="str">
-        <f t="shared" ref="D17:D61" si="5">IF(A17&lt;&gt;"",TRIM(A17),"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="E17" t="str">
-        <f t="shared" ref="E17:E61" si="6">IF(B17&lt;&gt;"",TRIM(B17),"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F17" t="str">
@@ -2206,11 +2149,11 @@
         <v/>
       </c>
       <c r="G37" t="str">
-        <f>IF($D37&lt;&gt;"",LOWER(CONCATENATE(LEFT($D37,1),G$1,$E37,"@",$O$2)),"")</f>
+        <f t="shared" ref="G37:G86" si="7">IF($D37&lt;&gt;"",LOWER(CONCATENATE(LEFT($D37,1),G$1,$E37,"@",$O$2)),"")</f>
         <v/>
       </c>
       <c r="H37" t="str">
-        <f>IF($D37&lt;&gt;"",LOWER((CONCATENATE($D37,H$1,$E37,"@",$O$2))),"")</f>
+        <f t="shared" ref="H37:H86" si="8">IF($D37&lt;&gt;"",(CONCATENATE($D37,H$1,$E37,"@",$O$2)),"")</f>
         <v/>
       </c>
       <c r="I37" t="str">
@@ -2248,11 +2191,11 @@
         <v/>
       </c>
       <c r="G38" t="str">
-        <f>IF($D38&lt;&gt;"",LOWER(CONCATENATE(LEFT($D38,1),G$1,$E38,"@",$O$2)),"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="H38" t="str">
-        <f>IF($D38&lt;&gt;"",LOWER((CONCATENATE($D38,H$1,$E38,"@",$O$2))),"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I38" t="str">
@@ -2290,11 +2233,11 @@
         <v/>
       </c>
       <c r="G39" t="str">
-        <f>IF($D39&lt;&gt;"",LOWER(CONCATENATE(LEFT($D39,1),G$1,$E39,"@",$O$2)),"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="H39" t="str">
-        <f>IF($D39&lt;&gt;"",LOWER((CONCATENATE($D39,H$1,$E39,"@",$O$2))),"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I39" t="str">
@@ -2332,11 +2275,11 @@
         <v/>
       </c>
       <c r="G40" t="str">
-        <f>IF($D40&lt;&gt;"",LOWER(CONCATENATE(LEFT($D40,1),G$1,$E40,"@",$O$2)),"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="H40" t="str">
-        <f>IF($D40&lt;&gt;"",LOWER((CONCATENATE($D40,H$1,$E40,"@",$O$2))),"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I40" t="str">
@@ -2374,11 +2317,11 @@
         <v/>
       </c>
       <c r="G41" t="str">
-        <f>IF($D41&lt;&gt;"",LOWER(CONCATENATE(LEFT($D41,1),G$1,$E41,"@",$O$2)),"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="H41" t="str">
-        <f>IF($D41&lt;&gt;"",LOWER((CONCATENATE($D41,H$1,$E41,"@",$O$2))),"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I41" t="str">
@@ -2416,11 +2359,11 @@
         <v/>
       </c>
       <c r="G42" t="str">
-        <f t="shared" ref="G42:G91" si="7">IF($D42&lt;&gt;"",LOWER(CONCATENATE(LEFT($D42,1),G$1,$E42,"@",$O$2)),"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="H42" t="str">
-        <f t="shared" ref="H42:H91" si="8">IF($D42&lt;&gt;"",(CONCATENATE($D42,H$1,$E42,"@",$O$2)),"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I42" t="str">
@@ -2790,7 +2733,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <f>IF($D51&lt;&gt;"",_xlfn.CONCAT(A51,"@",$O$2),"")</f>
+        <f t="shared" ref="F51:F114" si="9">IF($D51&lt;&gt;"",_xlfn.CONCAT(A51,"@",$O$2),"")</f>
         <v/>
       </c>
       <c r="G51" t="str">
@@ -2832,7 +2775,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <f>IF($D52&lt;&gt;"",_xlfn.CONCAT(A52,"@",$O$2),"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G52" t="str">
@@ -2874,7 +2817,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <f>IF($D53&lt;&gt;"",_xlfn.CONCAT(A53,"@",$O$2),"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G53" t="str">
@@ -2916,7 +2859,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <f>IF($D54&lt;&gt;"",_xlfn.CONCAT(A54,"@",$O$2),"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G54" t="str">
@@ -2958,7 +2901,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <f>IF($D55&lt;&gt;"",_xlfn.CONCAT(A55,"@",$O$2),"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G55" t="str">
@@ -3000,7 +2943,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <f t="shared" ref="F56:F119" si="9">IF($D56&lt;&gt;"",_xlfn.CONCAT(A56,"@",$O$2),"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G56" t="str">
@@ -3034,11 +2977,11 @@
     </row>
     <row r="57" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="D57:D106" si="10">IF(A57&lt;&gt;"",TRIM(A57),"")</f>
         <v/>
       </c>
       <c r="E57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="E57:E106" si="11">IF(B57&lt;&gt;"",TRIM(B57),"")</f>
         <v/>
       </c>
       <c r="F57" t="str">
@@ -3076,11 +3019,11 @@
     </row>
     <row r="58" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D58" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="E58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="F58" t="str">
@@ -3118,11 +3061,11 @@
     </row>
     <row r="59" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D59" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="E59" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="F59" t="str">
@@ -3160,11 +3103,11 @@
     </row>
     <row r="60" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D60" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="E60" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="F60" t="str">
@@ -3202,11 +3145,11 @@
     </row>
     <row r="61" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D61" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="E61" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="F61" t="str">
@@ -3244,11 +3187,11 @@
     </row>
     <row r="62" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D62" t="str">
-        <f t="shared" ref="D62:D111" si="10">IF(A62&lt;&gt;"",TRIM(A62),"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="E62" t="str">
-        <f t="shared" ref="E62:E111" si="11">IF(B62&lt;&gt;"",TRIM(B62),"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="F62" t="str">
@@ -3322,7 +3265,7 @@
         <v/>
       </c>
       <c r="M63" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="M63:M74" si="12">IF($D63&lt;&gt;"",LOWER(CONCATENATE($D63,M$1,LEFT($E63,1),"@",$O$2)),"")</f>
         <v/>
       </c>
     </row>
@@ -3364,7 +3307,7 @@
         <v/>
       </c>
       <c r="M64" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -3406,7 +3349,7 @@
         <v/>
       </c>
       <c r="M65" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -3448,7 +3391,7 @@
         <v/>
       </c>
       <c r="M66" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -3490,7 +3433,7 @@
         <v/>
       </c>
       <c r="M67" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -3532,7 +3475,7 @@
         <v/>
       </c>
       <c r="M68" t="str">
-        <f t="shared" ref="M68:M79" si="12">IF($D68&lt;&gt;"",LOWER(CONCATENATE($D68,M$1,LEFT($E68,1),"@",$O$2)),"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -3825,10 +3768,6 @@
         <f>IF($D75&lt;&gt;"",LOWER(CONCATENATE($D75,L$1,$E75,"@",$O$2)),"")</f>
         <v/>
       </c>
-      <c r="M75" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
     </row>
     <row r="76" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D76" t="str">
@@ -3867,10 +3806,6 @@
         <f>IF($D76&lt;&gt;"",LOWER(CONCATENATE($D76,L$1,$E76,"@",$O$2)),"")</f>
         <v/>
       </c>
-      <c r="M76" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
     </row>
     <row r="77" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D77" t="str">
@@ -3909,10 +3844,6 @@
         <f>IF($D77&lt;&gt;"",LOWER(CONCATENATE($D77,L$1,$E77,"@",$O$2)),"")</f>
         <v/>
       </c>
-      <c r="M77" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
     </row>
     <row r="78" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D78" t="str">
@@ -3951,10 +3882,6 @@
         <f>IF($D78&lt;&gt;"",LOWER(CONCATENATE($D78,L$1,$E78,"@",$O$2)),"")</f>
         <v/>
       </c>
-      <c r="M78" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
     </row>
     <row r="79" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D79" t="str">
@@ -3993,10 +3920,6 @@
         <f>IF($D79&lt;&gt;"",LOWER(CONCATENATE($D79,L$1,$E79,"@",$O$2)),"")</f>
         <v/>
       </c>
-      <c r="M79" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
     </row>
     <row r="80" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D80" t="str">
@@ -4278,11 +4201,11 @@
         <v/>
       </c>
       <c r="G87" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="G87:G119" si="13">IF($D87&lt;&gt;"",LOWER(CONCATENATE(LEFT($D87,1),G$1,$E87,"@",$O$2)),"")</f>
         <v/>
       </c>
       <c r="H87" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="H87:H119" si="14">IF($D87&lt;&gt;"",(CONCATENATE($D87,H$1,$E87,"@",$O$2)),"")</f>
         <v/>
       </c>
       <c r="I87" t="str">
@@ -4316,11 +4239,11 @@
         <v/>
       </c>
       <c r="G88" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="H88" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="I88" t="str">
@@ -4354,11 +4277,11 @@
         <v/>
       </c>
       <c r="G89" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="H89" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="I89" t="str">
@@ -4392,11 +4315,11 @@
         <v/>
       </c>
       <c r="G90" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="H90" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="I90" t="str">
@@ -4430,11 +4353,11 @@
         <v/>
       </c>
       <c r="G91" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="H91" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="I91" t="str">
@@ -4468,11 +4391,11 @@
         <v/>
       </c>
       <c r="G92" t="str">
-        <f t="shared" ref="G92:G124" si="13">IF($D92&lt;&gt;"",LOWER(CONCATENATE(LEFT($D92,1),G$1,$E92,"@",$O$2)),"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="H92" t="str">
-        <f t="shared" ref="H92:H124" si="14">IF($D92&lt;&gt;"",(CONCATENATE($D92,H$1,$E92,"@",$O$2)),"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="I92" t="str">
@@ -4902,11 +4825,7 @@
         <v/>
       </c>
       <c r="K103" t="str">
-        <f>IF($D103&lt;&gt;"",LOWER(CONCATENATE($D103,K$1,$E103,"@",$O$2)),"")</f>
-        <v/>
-      </c>
-      <c r="L103" t="str">
-        <f>IF($D103&lt;&gt;"",LOWER(CONCATENATE($D103,L$1,$E103,"@",$O$2)),"")</f>
+        <f t="shared" ref="K103:K119" si="15">IF($D103&lt;&gt;"",LOWER(CONCATENATE($D103,K$1,$E103,"@",$O$2)),"")</f>
         <v/>
       </c>
     </row>
@@ -4940,11 +4859,7 @@
         <v/>
       </c>
       <c r="K104" t="str">
-        <f>IF($D104&lt;&gt;"",LOWER(CONCATENATE($D104,K$1,$E104,"@",$O$2)),"")</f>
-        <v/>
-      </c>
-      <c r="L104" t="str">
-        <f>IF($D104&lt;&gt;"",LOWER(CONCATENATE($D104,L$1,$E104,"@",$O$2)),"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -4978,11 +4893,7 @@
         <v/>
       </c>
       <c r="K105" t="str">
-        <f>IF($D105&lt;&gt;"",LOWER(CONCATENATE($D105,K$1,$E105,"@",$O$2)),"")</f>
-        <v/>
-      </c>
-      <c r="L105" t="str">
-        <f>IF($D105&lt;&gt;"",LOWER(CONCATENATE($D105,L$1,$E105,"@",$O$2)),"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -5016,21 +4927,17 @@
         <v/>
       </c>
       <c r="K106" t="str">
-        <f>IF($D106&lt;&gt;"",LOWER(CONCATENATE($D106,K$1,$E106,"@",$O$2)),"")</f>
-        <v/>
-      </c>
-      <c r="L106" t="str">
-        <f>IF($D106&lt;&gt;"",LOWER(CONCATENATE($D106,L$1,$E106,"@",$O$2)),"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="107" spans="4:12" x14ac:dyDescent="0.3">
       <c r="D107" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="D107:D119" si="16">IF(A107&lt;&gt;"",TRIM(A107),"")</f>
         <v/>
       </c>
       <c r="E107" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="E107:E119" si="17">IF(B107&lt;&gt;"",TRIM(B107),"")</f>
         <v/>
       </c>
       <c r="F107" t="str">
@@ -5054,21 +4961,17 @@
         <v/>
       </c>
       <c r="K107" t="str">
-        <f>IF($D107&lt;&gt;"",LOWER(CONCATENATE($D107,K$1,$E107,"@",$O$2)),"")</f>
-        <v/>
-      </c>
-      <c r="L107" t="str">
-        <f>IF($D107&lt;&gt;"",LOWER(CONCATENATE($D107,L$1,$E107,"@",$O$2)),"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="108" spans="4:12" x14ac:dyDescent="0.3">
       <c r="D108" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="E108" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="F108" t="str">
@@ -5092,17 +4995,17 @@
         <v/>
       </c>
       <c r="K108" t="str">
-        <f t="shared" ref="K108:K124" si="15">IF($D108&lt;&gt;"",LOWER(CONCATENATE($D108,K$1,$E108,"@",$O$2)),"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="109" spans="4:12" x14ac:dyDescent="0.3">
       <c r="D109" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="E109" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="F109" t="str">
@@ -5132,11 +5035,11 @@
     </row>
     <row r="110" spans="4:12" x14ac:dyDescent="0.3">
       <c r="D110" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="E110" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="F110" t="str">
@@ -5166,11 +5069,11 @@
     </row>
     <row r="111" spans="4:12" x14ac:dyDescent="0.3">
       <c r="D111" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="E111" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="F111" t="str">
@@ -5200,11 +5103,11 @@
     </row>
     <row r="112" spans="4:12" x14ac:dyDescent="0.3">
       <c r="D112" t="str">
-        <f t="shared" ref="D112:D124" si="16">IF(A112&lt;&gt;"",TRIM(A112),"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="E112" t="str">
-        <f t="shared" ref="E112:E124" si="17">IF(B112&lt;&gt;"",TRIM(B112),"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="F112" t="str">
@@ -5310,7 +5213,7 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="F115:F118" si="18">IF($D115&lt;&gt;"",_xlfn.CONCAT(A115,"@",$O$2),"")</f>
         <v/>
       </c>
       <c r="G115" t="str">
@@ -5344,7 +5247,7 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="G116" t="str">
@@ -5378,7 +5281,7 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="G117" t="str">
@@ -5412,7 +5315,7 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="G118" t="str">
@@ -5445,10 +5348,6 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="F119" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
       <c r="G119" t="str">
         <f t="shared" si="13"/>
         <v/>
@@ -5466,172 +5365,6 @@
         <v/>
       </c>
       <c r="K119" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="120" spans="4:11" x14ac:dyDescent="0.3">
-      <c r="D120" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="E120" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="F120" t="str">
-        <f t="shared" ref="F120:F123" si="18">IF($D120&lt;&gt;"",_xlfn.CONCAT(A120,"@",$O$2),"")</f>
-        <v/>
-      </c>
-      <c r="G120" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H120" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="I120" t="str">
-        <f>IF($D120&lt;&gt;"",LOWER(CONCATENATE(LEFT($D120,1),I$1,$E120,"@",$O$2)),"")</f>
-        <v/>
-      </c>
-      <c r="J120" t="str">
-        <f>IF($D120&lt;&gt;"",LOWER(CONCATENATE(LEFT($D120,1),J$1,$E120,"@",$O$2)),"")</f>
-        <v/>
-      </c>
-      <c r="K120" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="121" spans="4:11" x14ac:dyDescent="0.3">
-      <c r="D121" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="E121" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="F121" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="G121" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H121" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="I121" t="str">
-        <f>IF($D121&lt;&gt;"",LOWER(CONCATENATE(LEFT($D121,1),I$1,$E121,"@",$O$2)),"")</f>
-        <v/>
-      </c>
-      <c r="J121" t="str">
-        <f>IF($D121&lt;&gt;"",LOWER(CONCATENATE(LEFT($D121,1),J$1,$E121,"@",$O$2)),"")</f>
-        <v/>
-      </c>
-      <c r="K121" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="122" spans="4:11" x14ac:dyDescent="0.3">
-      <c r="D122" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="E122" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="F122" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="G122" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H122" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="I122" t="str">
-        <f>IF($D122&lt;&gt;"",LOWER(CONCATENATE(LEFT($D122,1),I$1,$E122,"@",$O$2)),"")</f>
-        <v/>
-      </c>
-      <c r="J122" t="str">
-        <f>IF($D122&lt;&gt;"",LOWER(CONCATENATE(LEFT($D122,1),J$1,$E122,"@",$O$2)),"")</f>
-        <v/>
-      </c>
-      <c r="K122" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="123" spans="4:11" x14ac:dyDescent="0.3">
-      <c r="D123" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="E123" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="F123" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="G123" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H123" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="I123" t="str">
-        <f>IF($D123&lt;&gt;"",LOWER(CONCATENATE(LEFT($D123,1),I$1,$E123,"@",$O$2)),"")</f>
-        <v/>
-      </c>
-      <c r="J123" t="str">
-        <f>IF($D123&lt;&gt;"",LOWER(CONCATENATE(LEFT($D123,1),J$1,$E123,"@",$O$2)),"")</f>
-        <v/>
-      </c>
-      <c r="K123" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="124" spans="4:11" x14ac:dyDescent="0.3">
-      <c r="D124" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="E124" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="G124" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H124" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="I124" t="str">
-        <f>IF($D124&lt;&gt;"",LOWER(CONCATENATE(LEFT($D124,1),I$1,$E124,"@",$O$2)),"")</f>
-        <v/>
-      </c>
-      <c r="J124" t="str">
-        <f>IF($D124&lt;&gt;"",LOWER(CONCATENATE(LEFT($D124,1),J$1,$E124,"@",$O$2)),"")</f>
-        <v/>
-      </c>
-      <c r="K124" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
